--- a/resultados/third_review/20260907_data2024_sigtap_codes.xlsx
+++ b/resultados/third_review/20260907_data2024_sigtap_codes.xlsx
@@ -473,10 +473,10 @@
         <v>9</v>
       </c>
       <c r="E2" t="n">
-        <v>15626</v>
+        <v>17624</v>
       </c>
       <c r="F2" t="n">
-        <v>2021</v>
+        <v>2097</v>
       </c>
     </row>
     <row r="3">
@@ -493,10 +493,10 @@
         <v>13</v>
       </c>
       <c r="E3" t="n">
-        <v>339</v>
+        <v>385</v>
       </c>
       <c r="F3" t="n">
-        <v>49</v>
+        <v>54</v>
       </c>
     </row>
     <row r="4">
@@ -513,10 +513,10 @@
         <v>16</v>
       </c>
       <c r="E4" t="n">
-        <v>2359</v>
+        <v>2560</v>
       </c>
       <c r="F4" t="n">
-        <v>321</v>
+        <v>338</v>
       </c>
     </row>
     <row r="5">
@@ -533,10 +533,10 @@
         <v>19</v>
       </c>
       <c r="E5" t="n">
-        <v>5938</v>
+        <v>8226</v>
       </c>
       <c r="F5" t="n">
-        <v>814</v>
+        <v>976</v>
       </c>
     </row>
     <row r="6">
@@ -553,10 +553,10 @@
         <v>23</v>
       </c>
       <c r="E6" t="n">
-        <v>653</v>
+        <v>711</v>
       </c>
       <c r="F6" t="n">
-        <v>83</v>
+        <v>90</v>
       </c>
     </row>
     <row r="7">
@@ -573,10 +573,10 @@
         <v>26</v>
       </c>
       <c r="E7" t="n">
-        <v>6497</v>
+        <v>7359</v>
       </c>
       <c r="F7" t="n">
-        <v>814</v>
+        <v>885</v>
       </c>
     </row>
     <row r="8">
@@ -593,10 +593,10 @@
         <v>29</v>
       </c>
       <c r="E8" t="n">
-        <v>7130</v>
+        <v>8996</v>
       </c>
       <c r="F8" t="n">
-        <v>900</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="9">
